--- a/output/graficos_dimensiones/comunal_e_preneta_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2020_biobio.xlsx
@@ -114,27 +114,27 @@
     <t xml:space="preserve">Antuco</t>
   </si>
   <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de la Paz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro de la Paz</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:49</t>
+    <t xml:space="preserve">2026-09-09 23:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1016,7 +1016,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8205</v>
+        <v>8111</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1029,7 +1029,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8201</v>
+        <v>8108</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -1042,7 +1042,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8305</v>
+        <v>8102</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1055,7 +1055,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8102</v>
+        <v>8201</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1068,7 +1068,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>8108</v>
+        <v>8305</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1081,7 +1081,7 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8112</v>
+        <v>8205</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1094,7 +1094,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8111</v>
+        <v>8112</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_preneta_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:50</t>
+    <t xml:space="preserve">2026-09-18 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
